--- a/file_upload_forms/047_unemployment_claim_termination_appeal_form--file_upload_forms.xlsx
+++ b/file_upload_forms/047_unemployment_claim_termination_appeal_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'layoff'}</t>
+          <t>layoff</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Layoff'}</t>
+          <t>Layoff</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'redeployment'}</t>
+          <t>redeployment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Redeployment'}</t>
+          <t>Redeployment</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'retirement'}</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Retirement'}</t>
+          <t>Retirement</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'resignation'}</t>
+          <t>resignation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Resignation'}</t>
+          <t>Resignation</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'death'}</t>
+          <t>death</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Death'}</t>
+          <t>Death</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'disability'}</t>
+          <t>disability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Disability'}</t>
+          <t>Disability</t>
         </is>
       </c>
     </row>
